--- a/sheets/조재수대금교본/검수/바램.xlsx
+++ b/sheets/조재수대금교본/검수/바램.xlsx
@@ -5712,8 +5712,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5806,11 +5805,7 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="96.05" customHeight="true">
@@ -5850,11 +5845,7 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21"/>
       <c r="G6" s="22"/>
@@ -6034,7 +6025,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∧
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
@@ -6067,8 +6058,7 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -6324,16 +6314,14 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -6396,7 +6384,7 @@
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∧ㅂ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C19" s="24"/>
@@ -6445,8 +6433,7 @@
       <c r="C20" s="22"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E20" s="22"/>
@@ -6469,7 +6456,7 @@
       <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–㴌∽</t>
+–㴌</t>
         </is>
       </c>
       <c r="M20" s="22"/>
@@ -6482,16 +6469,15 @@
       <c r="A21" s="0"/>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">無ㅈ
-·
-ㄴ</t>
+          <t xml:space="preserve">無
+·</t>
         </is>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-湳∽</t>
+湳</t>
         </is>
       </c>
       <c r="E21" s="23"/>
@@ -6519,8 +6505,7 @@
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M21" s="23"/>
@@ -6604,11 +6589,7 @@
         </is>
       </c>
       <c r="K23" s="22"/>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L23" s="21"/>
       <c r="M23" s="22"/>
       <c r="N23" s="21" t="inlineStr">
         <is>
@@ -6713,16 +6694,14 @@
       <c r="M25" s="24"/>
       <c r="N25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -6762,7 +6741,7 @@
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O26" s="22"/>

--- a/sheets/조재수대금교본/검수/바램.xlsx
+++ b/sheets/조재수대금교본/검수/바램.xlsx
@@ -5805,7 +5805,11 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="96.05" customHeight="true">
@@ -5845,7 +5849,11 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E6" s="22"/>
       <c r="F6" s="21"/>
       <c r="G6" s="22"/>
@@ -6025,7 +6033,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢∧
 南</t>
         </is>
       </c>
@@ -6384,7 +6392,7 @@
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∧ㅂ</t>
         </is>
       </c>
       <c r="C19" s="24"/>
@@ -6456,7 +6464,7 @@
       <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–㴌</t>
+–㴌∽</t>
         </is>
       </c>
       <c r="M20" s="22"/>
@@ -6470,14 +6478,15 @@
       <c r="B21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-·</t>
+·
+ㄴ</t>
         </is>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-湳</t>
+湳∽</t>
         </is>
       </c>
       <c r="E21" s="23"/>
@@ -6741,7 +6750,7 @@
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="O26" s="22"/>

--- a/sheets/조재수대금교본/검수/바램.xlsx
+++ b/sheets/조재수대금교본/검수/바램.xlsx
@@ -5656,28 +5656,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -6216,7 +6216,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -6261,7 +6261,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="64.52" customHeight="true">
+    <row r="16" ht="74.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="96.05" customHeight="true">
+    <row r="17" ht="110.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="96.05" customHeight="true">
+    <row r="18" ht="110.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="96.05" customHeight="true">
+    <row r="19" ht="110.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="96.05" customHeight="true">
+    <row r="20" ht="110.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="96.05" customHeight="true">
+    <row r="21" ht="110.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="25" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="96.05" customHeight="true">
+    <row r="22" ht="110.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="96.05" customHeight="true">
+    <row r="23" ht="110.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="96.05" customHeight="true">
+    <row r="24" ht="110.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="96.05" customHeight="true">
+    <row r="25" ht="110.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="96.05" customHeight="true">
+    <row r="26" ht="110.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="96.05" customHeight="true">
+    <row r="27" ht="110.36" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6794,7 +6794,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="96.05" customHeight="true">
+    <row r="28" ht="110.36" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
